--- a/inspiired_test/clone_info.xlsx
+++ b/inspiired_test/clone_info.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gbedwell/Documents/github/intmap/inspiired_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70DF38E-D0E7-DB43-AB09-D9EAAC20BF50}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9560D9CC-81DE-664D-ACE1-98F68DF8E63C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{31A990DB-335A-C847-8705-EB0104C1E28E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{31A990DB-335A-C847-8705-EB0104C1E28E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="38">
   <si>
     <t>clone</t>
   </si>
@@ -51,15 +51,6 @@
     <t>strand</t>
   </si>
   <si>
-    <t>clone_count</t>
-  </si>
-  <si>
-    <t>total_count</t>
-  </si>
-  <si>
-    <t>clone_fraction</t>
-  </si>
-  <si>
     <t>expected_frac</t>
   </si>
   <si>
@@ -103,6 +94,60 @@
   </si>
   <si>
     <t>original_expected</t>
+  </si>
+  <si>
+    <t>rep1</t>
+  </si>
+  <si>
+    <t>rep2</t>
+  </si>
+  <si>
+    <t>rep3</t>
+  </si>
+  <si>
+    <t>rep4</t>
+  </si>
+  <si>
+    <t>clone_frac</t>
+  </si>
+  <si>
+    <t>clone_sd</t>
+  </si>
+  <si>
+    <t>inspiired_frac</t>
+  </si>
+  <si>
+    <t>inspiired_sd</t>
+  </si>
+  <si>
+    <t>isseq_frac</t>
+  </si>
+  <si>
+    <t>isseq_sd</t>
+  </si>
+  <si>
+    <t>inspiired_rep1</t>
+  </si>
+  <si>
+    <t>inspiired_rep2</t>
+  </si>
+  <si>
+    <t>inspiired_rep3</t>
+  </si>
+  <si>
+    <t>inspiired_rep4</t>
+  </si>
+  <si>
+    <t>isseq_rep1</t>
+  </si>
+  <si>
+    <t>isseq_rep2</t>
+  </si>
+  <si>
+    <t>isseq_rep3</t>
+  </si>
+  <si>
+    <t>isseq_rep4</t>
   </si>
 </sst>
 </file>
@@ -468,16 +513,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F5FA7E-8C90-564C-B41B-867D0B532DD3}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,926 +538,2322 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>52699701</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <f>18+8+19+25</f>
-        <v>70</v>
+        <f>18/18</f>
+        <v>1</v>
       </c>
       <c r="G2">
-        <f>SUM($F$2:$F$3)</f>
-        <v>71</v>
+        <f>8/8</f>
+        <v>1</v>
       </c>
       <c r="H2">
-        <f>F2/G2</f>
-        <v>0.9859154929577465</v>
+        <f>19/19</f>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <f>25/26</f>
+        <v>0.96153846153846156</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <f>AVERAGE(F2:I2)</f>
+        <v>0.99038461538461542</v>
+      </c>
+      <c r="K2">
+        <f>STDEV(F2:I2)</f>
+        <v>1.9230769230769218E-2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0.97058823529411764</v>
+      </c>
+      <c r="R2">
+        <v>0.99264705882352944</v>
+      </c>
+      <c r="S2">
+        <v>1.470588235294118E-2</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="X2">
+        <v>0.99193548387096775</v>
+      </c>
+      <c r="Y2">
+        <v>1.6129032258064502E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <f>0/18</f>
+        <v>0</v>
       </c>
       <c r="G3">
-        <f>SUM($F$2:$F$3)</f>
-        <v>71</v>
+        <f>0/8</f>
+        <v>0</v>
       </c>
       <c r="H3">
-        <f>F3/G3</f>
-        <v>1.4084507042253521E-2</v>
+        <f>0/19</f>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <f>1/26</f>
+        <v>3.8461538461538464E-2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <f>AVERAGE(F3:I3)</f>
+        <v>9.6153846153846159E-3</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K29" si="0">STDEV(F3:I3)</f>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>2.9411764705882353E-2</v>
+      </c>
+      <c r="R3">
+        <v>7.3529411764705881E-3</v>
+      </c>
+      <c r="S3">
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="X3">
+        <v>8.0645161290322578E-3</v>
+      </c>
+      <c r="Y3">
+        <v>1.6129032258064516E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>77440128</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <f>30+39+51+44</f>
-        <v>164</v>
+        <f>30/30</f>
+        <v>1</v>
       </c>
       <c r="G4">
-        <f>SUM($F$4:$F$5)</f>
-        <v>167</v>
+        <f>39/39</f>
+        <v>1</v>
       </c>
       <c r="H4">
-        <f>F4/G4</f>
-        <v>0.98203592814371254</v>
+        <f>54/54</f>
+        <v>1</v>
       </c>
       <c r="I4">
+        <f>44/44</f>
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <f>AVERAGE(F4:I4)</f>
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <f>0/30</f>
+        <v>0</v>
       </c>
       <c r="G5">
-        <f>SUM($F$4:$F$5)</f>
-        <v>167</v>
+        <f>0/39</f>
+        <v>0</v>
       </c>
       <c r="H5">
-        <f>F5/G5</f>
-        <v>1.7964071856287425E-2</v>
+        <f>0/54</f>
+        <v>0</v>
       </c>
       <c r="I5">
+        <f>0/44</f>
         <v>0</v>
       </c>
       <c r="J5">
+        <f>AVERAGE(F5:I5)</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>1330530</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <f>21+15+20+11</f>
-        <v>67</v>
+        <f>21/22</f>
+        <v>0.95454545454545459</v>
       </c>
       <c r="G6">
-        <f>SUM($F$6:$F$7)</f>
-        <v>69</v>
+        <f>15/16</f>
+        <v>0.9375</v>
       </c>
       <c r="H6">
-        <f t="shared" ref="H6:H11" si="0">F6/G6</f>
-        <v>0.97101449275362317</v>
+        <f>20/20</f>
+        <v>1</v>
       </c>
       <c r="I6">
+        <f>11/11</f>
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <f t="shared" ref="J6:J29" si="1">AVERAGE(F6:I6)</f>
+        <v>0.97301136363636365</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>3.1931278977438186E-2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.96875</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0.9921875</v>
+      </c>
+      <c r="S6">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <f>1/22</f>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="G7">
-        <f>SUM($F$6:$F$7)</f>
-        <v>69</v>
+        <f>1/16</f>
+        <v>6.25E-2</v>
       </c>
       <c r="H7">
+        <f>0/20</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f>0/11</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>2.6988636363636364E-2</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="0"/>
-        <v>2.8985507246376812E-2</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+        <v>3.1931278977438193E-2</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>3.125E-2</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="S7">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>153461600</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <f>31+36+42+49</f>
-        <v>158</v>
+        <f>31/31</f>
+        <v>1</v>
       </c>
       <c r="G8">
-        <f>SUM($F$8:$F$9)</f>
-        <v>158</v>
+        <f>36/36</f>
+        <v>1</v>
       </c>
       <c r="H8">
+        <f>42/43</f>
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="I8">
+        <f>49/49</f>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>0.9941860465116279</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+        <v>1.1627906976744207E-2</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0.99596774193548387</v>
+      </c>
+      <c r="S8">
+        <v>8.0645161290322509E-3</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.99444444444444446</v>
+      </c>
+      <c r="Y8">
+        <v>1.1111111111111127E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="F9">
+        <f>0/31</f>
         <v>0</v>
       </c>
       <c r="G9">
-        <f>SUM($F$8:$F$9)</f>
-        <v>158</v>
+        <f>0/36</f>
+        <v>0</v>
       </c>
       <c r="H9">
+        <f>1/43</f>
+        <v>2.3255813953488372E-2</v>
+      </c>
+      <c r="I9">
+        <f>0/49</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>5.8139534883720929E-3</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
+        <v>1.1627906976744186E-2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.6129032258064516E-2</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>4.0322580645161289E-3</v>
+      </c>
+      <c r="S9">
+        <v>8.0645161290322578E-3</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>5.5555555555555558E-3</v>
+      </c>
+      <c r="Y9">
+        <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>148889089</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <f>2+1+1+2</f>
-        <v>6</v>
+        <f>2/2</f>
+        <v>1</v>
       </c>
       <c r="G10">
-        <f>SUM($F$10:$F$11)</f>
-        <v>6</v>
+        <f>1/1</f>
+        <v>1</v>
       </c>
       <c r="H10">
+        <f>1/1</f>
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <f>2/2</f>
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K10">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="F11">
+        <f>0/2</f>
         <v>0</v>
       </c>
       <c r="G11">
-        <f>SUM($F$10:$F$11)</f>
-        <v>6</v>
+        <f>0/1</f>
+        <v>0</v>
       </c>
       <c r="H11">
+        <f>0/1</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f>0/2</f>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>14</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
       </c>
       <c r="D12">
         <v>52699701</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <f>2+2+7+4</f>
+        <f>2/SUM(2,8,8,9,11)</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="G12">
+        <f>2/SUM(2,9,10,6,6)</f>
+        <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="H12">
+        <f>7/SUM(7,8,9,5,7)</f>
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="I12">
+        <f>4/SUM(4,3,4,8,8)</f>
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>0.1139575580365054</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>6.8930867118533745E-2</v>
+      </c>
+      <c r="L12">
+        <v>0.2</v>
+      </c>
+      <c r="M12">
+        <v>0.2</v>
+      </c>
+      <c r="N12">
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="O12">
+        <v>4.6511627906976744E-2</v>
+      </c>
+      <c r="P12">
+        <v>0.21153846153846154</v>
+      </c>
+      <c r="Q12">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="R12">
+        <v>0.11949973463757441</v>
+      </c>
+      <c r="S12">
+        <v>8.7222576601791432E-2</v>
+      </c>
+      <c r="T12">
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="U12">
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="V12">
+        <v>0.20512820512820512</v>
+      </c>
+      <c r="W12">
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="X12">
+        <v>0.11673572997265989</v>
+      </c>
+      <c r="Y12">
+        <v>8.4854901314369818E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>148889089</v>
+      </c>
+      <c r="E13" t="s">
         <v>15</v>
       </c>
-      <c r="G12">
-        <f>SUM($F$12:$F$17)</f>
-        <v>134</v>
-      </c>
-      <c r="H12">
-        <f>F12/G12</f>
-        <v>0.11194029850746269</v>
-      </c>
-      <c r="I12">
+      <c r="F13">
+        <f>8/SUM(2,8,8,9,11)</f>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="G13">
+        <f>9/SUM(2,9,10,6,6)</f>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="H13">
+        <f>8/SUM(7,8,9,5,7)</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="I13">
+        <f>3/SUM(4,3,4,8,8)</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>0.20414673046251991</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>6.7642047467352653E-2</v>
+      </c>
+      <c r="L13">
         <v>0.2</v>
       </c>
-      <c r="J12">
+      <c r="M13">
         <v>0.2</v>
       </c>
+      <c r="N13">
+        <v>0.36956521739130432</v>
+      </c>
+      <c r="O13">
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="P13">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="Q13">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="R13">
+        <v>0.28828996792774819</v>
+      </c>
+      <c r="S13">
+        <v>5.7336699923369192E-2</v>
+      </c>
+      <c r="T13">
+        <v>0.45714285714285713</v>
+      </c>
+      <c r="U13">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="V13">
+        <v>0.35897435897435898</v>
+      </c>
+      <c r="W13">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="X13">
+        <v>0.32082574451873674</v>
+      </c>
+      <c r="Y13">
+        <v>0.10859415869240648</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13">
-        <v>77440128</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13">
-        <f>9+5+5+8</f>
-        <v>27</v>
-      </c>
-      <c r="G13">
-        <f t="shared" ref="G13:G17" si="1">SUM($F$12:$F$17)</f>
-        <v>134</v>
-      </c>
-      <c r="H13">
-        <f t="shared" ref="H13:H29" si="2">F13/G13</f>
-        <v>0.20149253731343283</v>
-      </c>
-      <c r="I13">
-        <v>0.2</v>
-      </c>
-      <c r="J13">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
       <c r="D14">
-        <v>1330530</v>
+        <v>153461600</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
       </c>
       <c r="F14">
-        <f>11+6+7+8</f>
-        <v>32</v>
+        <f>8/SUM(2,8,8,9,11)</f>
+        <v>0.21052631578947367</v>
       </c>
       <c r="G14">
+        <f>10/SUM(2,9,10,6,6)</f>
+        <v>0.30303030303030304</v>
+      </c>
+      <c r="H14">
+        <f>9/SUM(7,8,9,5,7)</f>
+        <v>0.25</v>
+      </c>
+      <c r="I14">
+        <f>4/SUM(4,3,4,8,8)</f>
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="J14">
         <f t="shared" si="1"/>
-        <v>134</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="2"/>
-        <v>0.23880597014925373</v>
-      </c>
-      <c r="I14">
+        <v>0.2279261917419812</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>6.5307407610067716E-2</v>
+      </c>
+      <c r="L14">
         <v>0.2</v>
       </c>
-      <c r="J14">
+      <c r="M14">
         <v>0.2</v>
       </c>
+      <c r="N14">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="O14">
+        <v>0.20930232558139536</v>
+      </c>
+      <c r="P14">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="Q14">
+        <v>8.8235294117647065E-2</v>
+      </c>
+      <c r="R14">
+        <v>0.19603992331940942</v>
+      </c>
+      <c r="S14">
+        <v>7.6617036373836392E-2</v>
+      </c>
+      <c r="T14">
+        <v>8.5714285714285715E-2</v>
+      </c>
+      <c r="U14">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="V14">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="W14">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="X14">
+        <v>0.14220379175885295</v>
+      </c>
+      <c r="Y14">
+        <v>6.2764118292829588E-2</v>
+      </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15">
-        <v>153461600</v>
+        <v>77440128</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <f>8+10+9+4</f>
-        <v>31</v>
+        <f>9/SUM(2,8,8,9,11)</f>
+        <v>0.23684210526315788</v>
       </c>
       <c r="G15">
+        <f>6/SUM(2,9,10,6,6)</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="H15">
+        <f>5/SUM(7,8,9,5,7)</f>
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="I15">
+        <f>8/SUM(4,3,4,8,8)</f>
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="J15">
         <f t="shared" si="1"/>
-        <v>134</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="2"/>
-        <v>0.23134328358208955</v>
-      </c>
-      <c r="I15">
+        <v>0.21346136806663124</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>6.8241312251293582E-2</v>
+      </c>
+      <c r="L15">
         <v>0.2</v>
       </c>
-      <c r="J15">
+      <c r="M15">
         <v>0.2</v>
       </c>
+      <c r="N15">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="O15">
+        <v>0.23255813953488372</v>
+      </c>
+      <c r="P15">
+        <v>9.6153846153846159E-2</v>
+      </c>
+      <c r="Q15">
+        <v>0.26470588235294118</v>
+      </c>
+      <c r="R15">
+        <v>0.19183272787998296</v>
+      </c>
+      <c r="S15">
+        <v>7.4037421382078097E-2</v>
+      </c>
+      <c r="T15">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="U15">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="V15">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="W15">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="X15">
+        <v>0.15173350935308666</v>
+      </c>
+      <c r="Y15">
+        <v>7.3335228509039632E-2</v>
+      </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
       </c>
       <c r="D16">
-        <v>148889089</v>
+        <v>1330530</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <f>8+9+8+3</f>
-        <v>28</v>
+        <f>11/SUM(2,8,8,9,11)</f>
+        <v>0.28947368421052633</v>
       </c>
       <c r="G16">
+        <f>6/SUM(2,9,10,6,6)</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="H16">
+        <f>7/SUM(7,8,9,5,7)</f>
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="I16">
+        <f>8/SUM(4,3,4,8,8)</f>
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="J16">
         <f t="shared" si="1"/>
-        <v>134</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="2"/>
-        <v>0.20895522388059701</v>
-      </c>
-      <c r="I16">
+        <v>0.24050815169236223</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>6.0762702766282754E-2</v>
+      </c>
+      <c r="L16">
         <v>0.2</v>
       </c>
-      <c r="J16">
+      <c r="M16">
         <v>0.2</v>
       </c>
+      <c r="N16">
+        <v>0.19565217391304349</v>
+      </c>
+      <c r="O16">
+        <v>0.23255813953488372</v>
+      </c>
+      <c r="P16">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="Q16">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="R16">
+        <v>0.204337646235285</v>
+      </c>
+      <c r="S16">
+        <v>3.8207885737033938E-2</v>
+      </c>
+      <c r="T16">
+        <v>0.25714285714285712</v>
+      </c>
+      <c r="U16">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="V16">
+        <v>0.17948717948717949</v>
+      </c>
+      <c r="W16">
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="X16">
+        <v>0.2685012243966638</v>
+      </c>
+      <c r="Y16">
+        <v>8.254311751635883E-2</v>
+      </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f>0/SUM(2,9,10,6,6)</f>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f>0/SUM(7,8,9,5,7)</f>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <f>0/SUM(4,3,4,8,8)</f>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>14</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <f>0+1+0+0</f>
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>134</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="2"/>
-        <v>7.462686567164179E-3</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
       </c>
       <c r="D18">
         <v>52699701</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <f>4+5+3+4</f>
-        <v>16</v>
+        <f>4/SUM(4,5,6,4,14)</f>
+        <v>0.12121212121212122</v>
       </c>
       <c r="G18">
-        <f>SUM($F$18:$F$23)</f>
-        <v>137</v>
+        <f>5/SUM(5,5,5,4,16,1)</f>
+        <v>0.1388888888888889</v>
       </c>
       <c r="H18">
-        <f t="shared" si="2"/>
-        <v>0.11678832116788321</v>
+        <f>3/SUM(3,8,9,8,15)</f>
+        <v>6.9767441860465115E-2</v>
       </c>
       <c r="I18">
+        <f>4/SUM(4,3,5,1,12)</f>
+        <v>0.16</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>0.1224671129903688</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>3.8545309582803278E-2</v>
+      </c>
+      <c r="L18">
         <v>0.2</v>
       </c>
-      <c r="J18">
+      <c r="M18">
         <v>0.2</v>
       </c>
+      <c r="N18">
+        <v>0.20370370370370369</v>
+      </c>
+      <c r="O18">
+        <v>0.25</v>
+      </c>
+      <c r="P18">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="Q18">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="R18">
+        <v>0.16539725209080047</v>
+      </c>
+      <c r="S18">
+        <v>7.3668442938935222E-2</v>
+      </c>
+      <c r="T18">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="U18">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="V18">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="W18">
+        <v>0.11363636363636363</v>
+      </c>
+      <c r="X18">
+        <v>0.17224624790414264</v>
+      </c>
+      <c r="Y18">
+        <v>8.0542366139643704E-2</v>
+      </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <v>148889089</v>
+      </c>
+      <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19">
-        <v>77440128</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
       <c r="F19">
-        <f>4+4+8+1</f>
-        <v>17</v>
+        <f>5/SUM(4,5,6,4,14)</f>
+        <v>0.15151515151515152</v>
       </c>
       <c r="G19">
-        <f t="shared" ref="G19:G23" si="3">SUM($F$18:$F$23)</f>
-        <v>137</v>
+        <f>5/SUM(5,5,5,4,16,1)</f>
+        <v>0.1388888888888889</v>
       </c>
       <c r="H19">
-        <f t="shared" si="2"/>
-        <v>0.12408759124087591</v>
+        <f>8/SUM(3,8,9,8,15)</f>
+        <v>0.18604651162790697</v>
       </c>
       <c r="I19">
+        <f>3/SUM(4,3,5,1,12)</f>
+        <v>0.12</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>0.14911263800798685</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>2.7820578891405028E-2</v>
+      </c>
+      <c r="L19">
         <v>0.1</v>
       </c>
-      <c r="J19">
+      <c r="M19">
         <v>0.1</v>
       </c>
+      <c r="N19">
+        <v>0.18518518518518517</v>
+      </c>
+      <c r="O19">
+        <v>0.11363636363636363</v>
+      </c>
+      <c r="P19">
+        <v>0.14516129032258066</v>
+      </c>
+      <c r="Q19">
+        <v>0.12962962962962962</v>
+      </c>
+      <c r="R19">
+        <v>0.14340311719343979</v>
+      </c>
+      <c r="S19">
+        <v>3.0684420343321778E-2</v>
+      </c>
+      <c r="T19">
+        <v>0.13461538461538461</v>
+      </c>
+      <c r="U19">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="V19">
+        <v>0.23684210526315788</v>
+      </c>
+      <c r="W19">
+        <v>0.15909090909090909</v>
+      </c>
+      <c r="X19">
+        <v>0.15347043307569622</v>
+      </c>
+      <c r="Y19">
+        <v>6.3919613804324607E-2</v>
+      </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D20">
-        <v>1330530</v>
+        <v>153461600</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
       </c>
       <c r="F20">
-        <f>14+16+15+12</f>
-        <v>57</v>
+        <f>6/SUM(4,5,6,4,14)</f>
+        <v>0.18181818181818182</v>
       </c>
       <c r="G20">
-        <f t="shared" si="3"/>
-        <v>137</v>
+        <f>5/SUM(5,5,5,4,16,1)</f>
+        <v>0.1388888888888889</v>
       </c>
       <c r="H20">
-        <f t="shared" si="2"/>
-        <v>0.41605839416058393</v>
+        <f>9/SUM(3,8,9,8,15)</f>
+        <v>0.20930232558139536</v>
       </c>
       <c r="I20">
-        <v>0.45</v>
+        <f>5/SUM(4,3,5,1,12)</f>
+        <v>0.2</v>
       </c>
       <c r="J20">
-        <v>0.45</v>
+        <f t="shared" si="1"/>
+        <v>0.18250234907211654</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>3.1235708854222586E-2</v>
+      </c>
+      <c r="L20">
+        <v>0.15</v>
+      </c>
+      <c r="M20">
+        <v>0.15</v>
+      </c>
+      <c r="N20">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="O20">
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="P20">
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="Q20">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="R20">
+        <v>0.13487699576409251</v>
+      </c>
+      <c r="S20">
+        <v>5.6172292467243409E-2</v>
+      </c>
+      <c r="T20">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="U20">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="V20">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="W20">
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="X20">
+        <v>0.12202746084325032</v>
+      </c>
+      <c r="Y20">
+        <v>7.3399237001948447E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>77440128</v>
+      </c>
+      <c r="E21" t="s">
         <v>15</v>
       </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21">
-        <v>153461600</v>
-      </c>
-      <c r="E21" t="s">
-        <v>21</v>
-      </c>
       <c r="F21">
-        <f>6+5+9+5</f>
-        <v>25</v>
+        <f>4/SUM(4,5,6,4,14)</f>
+        <v>0.12121212121212122</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
-        <v>137</v>
+        <f>4/SUM(5,5,5,4,16,1)</f>
+        <v>0.1111111111111111</v>
       </c>
       <c r="H21">
-        <f t="shared" si="2"/>
-        <v>0.18248175182481752</v>
+        <f>8/SUM(3,8,9,8,15)</f>
+        <v>0.18604651162790697</v>
       </c>
       <c r="I21">
-        <v>0.15</v>
+        <f>1/SUM(4,3,5,1,12)</f>
+        <v>0.04</v>
       </c>
       <c r="J21">
-        <v>0.15</v>
+        <f t="shared" si="1"/>
+        <v>0.11459243598778482</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>5.9793133071566924E-2</v>
+      </c>
+      <c r="L21">
+        <v>0.1</v>
+      </c>
+      <c r="M21">
+        <v>0.1</v>
+      </c>
+      <c r="N21">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="O21">
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="P21">
+        <v>0.14516129032258066</v>
+      </c>
+      <c r="Q21">
+        <v>0.12962962962962962</v>
+      </c>
+      <c r="R21">
+        <v>0.11352096231128489</v>
+      </c>
+      <c r="S21">
+        <v>3.3276843262920963E-2</v>
+      </c>
+      <c r="T21">
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="U21">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="V21">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="W21">
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="X21">
+        <v>7.2547335705230448E-2</v>
+      </c>
+      <c r="Y21">
+        <v>3.0865521444349824E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="1">
-        <v>148889089</v>
+      <c r="D22">
+        <v>1330530</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <f>5+5+8+3</f>
-        <v>21</v>
+        <f>14/SUM(4,5,6,4,14)</f>
+        <v>0.42424242424242425</v>
       </c>
       <c r="G22">
-        <f t="shared" si="3"/>
-        <v>137</v>
+        <f>16/SUM(5,5,5,4,16,1)</f>
+        <v>0.44444444444444442</v>
       </c>
       <c r="H22">
-        <f t="shared" si="2"/>
-        <v>0.15328467153284672</v>
+        <f>15/SUM(3,8,9,8,15)</f>
+        <v>0.34883720930232559</v>
       </c>
       <c r="I22">
-        <v>0.1</v>
+        <f>12/SUM(4,3,5,1,12)</f>
+        <v>0.48</v>
       </c>
       <c r="J22">
-        <v>0.1</v>
+        <f t="shared" si="1"/>
+        <v>0.42438101949729856</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>5.5386215132734111E-2</v>
+      </c>
+      <c r="L22">
+        <v>0.45</v>
+      </c>
+      <c r="M22">
+        <v>0.45</v>
+      </c>
+      <c r="N22">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O22">
+        <v>0.47727272727272729</v>
+      </c>
+      <c r="P22">
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="Q22">
+        <v>0.51851851851851849</v>
+      </c>
+      <c r="R22">
+        <v>0.43711985445856416</v>
+      </c>
+      <c r="S22">
+        <v>8.0260478978992286E-2</v>
+      </c>
+      <c r="T22">
+        <v>0.48076923076923078</v>
+      </c>
+      <c r="U22">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="V22">
+        <v>0.34210526315789475</v>
+      </c>
+      <c r="W22">
+        <v>0.56818181818181823</v>
+      </c>
+      <c r="X22">
+        <v>0.47970852247168039</v>
+      </c>
+      <c r="Y22">
+        <v>9.8444501175985508E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="F23">
-        <f>0+1+0+0</f>
-        <v>1</v>
+        <f>0/SUM(4,5,6,4,14)</f>
+        <v>0</v>
       </c>
       <c r="G23">
-        <f t="shared" si="3"/>
-        <v>137</v>
+        <f>1/SUM(5,5,5,4,16,1)</f>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="H23">
-        <f t="shared" si="2"/>
-        <v>7.2992700729927005E-3</v>
+        <f>0/SUM(3,8,9,8,15)</f>
+        <v>0</v>
       </c>
       <c r="I23">
+        <f>0/SUM(4,3,5,1,12)</f>
         <v>0</v>
       </c>
       <c r="J23">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>2.2727272727272728E-2</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>5.681818181818182E-3</v>
+      </c>
+      <c r="S23">
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D24">
         <v>52699701</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F24">
-        <f>1+1+0+3</f>
+        <f>1/SUM(1,18,1,4)</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G24">
+        <f>1/SUM(1,31,3,9)</f>
+        <v>2.2727272727272728E-2</v>
+      </c>
+      <c r="H24">
+        <f>0/SUM(0,23,2,3)</f>
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <f>3/SUM(3,17,4,4)</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>4.2884199134199136E-2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>4.610138729633146E-2</v>
+      </c>
+      <c r="L24">
+        <v>0.1</v>
+      </c>
+      <c r="M24">
+        <v>0.09</v>
+      </c>
+      <c r="N24">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="O24">
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="R24">
+        <v>4.7599595393713043E-2</v>
+      </c>
+      <c r="S24">
+        <v>4.9750031289138318E-2</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>4.6511627906976744E-2</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="X24">
+        <v>5.329457364341085E-2</v>
+      </c>
+      <c r="Y24">
+        <v>7.8697443814910659E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25">
         <v>5</v>
       </c>
-      <c r="G24">
-        <f>SUM($F$24:$F$29)</f>
-        <v>124</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="2"/>
-        <v>4.0322580645161289E-2</v>
-      </c>
-      <c r="I24">
-        <v>0.1</v>
-      </c>
-      <c r="J24">
-        <v>0.09</v>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25">
+        <v>148889089</v>
+      </c>
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25">
+        <f>18/SUM(1,18,1,4)</f>
+        <v>0.75</v>
+      </c>
+      <c r="G25">
+        <f>31/SUM(1,31,3,9)</f>
+        <v>0.70454545454545459</v>
+      </c>
+      <c r="H25">
+        <f>23/SUM(0,23,2,3)</f>
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="I25">
+        <f>17/SUM(3,17,4,4)</f>
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>0.72077922077922085</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>8.9742045201852055E-2</v>
+      </c>
+      <c r="L25">
+        <v>0.65</v>
+      </c>
+      <c r="M25">
+        <v>0.65</v>
+      </c>
+      <c r="N25">
+        <v>0.75</v>
+      </c>
+      <c r="O25">
+        <v>0.7592592592592593</v>
+      </c>
+      <c r="P25">
+        <v>0.70731707317073167</v>
+      </c>
+      <c r="Q25">
+        <v>0.61764705882352944</v>
+      </c>
+      <c r="R25">
+        <v>0.7085558478133801</v>
+      </c>
+      <c r="S25">
+        <v>6.4690020252829022E-2</v>
+      </c>
+      <c r="T25">
+        <v>0.84</v>
+      </c>
+      <c r="U25">
+        <v>0.72093023255813948</v>
+      </c>
+      <c r="V25">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="W25">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="X25">
+        <v>0.70620478036175705</v>
+      </c>
+      <c r="Y25">
+        <v>0.12308174660569503</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25">
-        <v>77440128</v>
-      </c>
-      <c r="E25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25">
-        <f>4+9+3+4</f>
-        <v>20</v>
-      </c>
-      <c r="G25">
-        <f t="shared" ref="G25:G29" si="4">SUM($F$24:$F$29)</f>
-        <v>124</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="2"/>
-        <v>0.16129032258064516</v>
-      </c>
-      <c r="I25">
-        <v>0.15</v>
-      </c>
-      <c r="J25">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>1330530</v>
+        <v>153461600</v>
       </c>
       <c r="E26" t="s">
         <v>18</v>
       </c>
       <c r="F26">
-        <f>0+0+0+0</f>
-        <v>0</v>
+        <f>1/SUM(1,18,1,4)</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="G26">
-        <f t="shared" si="4"/>
-        <v>124</v>
+        <f>3/SUM(1,31,3,9)</f>
+        <v>6.8181818181818177E-2</v>
       </c>
       <c r="H26">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>2/SUM(0,23,2,3)</f>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <f>4/SUM(3,17,4,4)</f>
+        <v>0.14285714285714285</v>
       </c>
       <c r="J26">
+        <f t="shared" si="1"/>
+        <v>8.1033549783549777E-2</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>4.331793608976197E-2</v>
+      </c>
+      <c r="L26">
         <v>0.1</v>
       </c>
+      <c r="M26">
+        <v>0.1</v>
+      </c>
+      <c r="N26">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="O26">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="P26">
+        <v>0.14634146341463414</v>
+      </c>
+      <c r="Q26">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="R26">
+        <v>9.7743162305572645E-2</v>
+      </c>
+      <c r="S26">
+        <v>4.1754088915947597E-2</v>
+      </c>
+      <c r="T26">
+        <v>0.08</v>
+      </c>
+      <c r="U26">
+        <v>4.6511627906976744E-2</v>
+      </c>
+      <c r="V26">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="W26">
+        <v>0.125</v>
+      </c>
+      <c r="X26">
+        <v>9.7600129198966407E-2</v>
+      </c>
+      <c r="Y26">
+        <v>4.2329320447838686E-2</v>
+      </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
         <v>16</v>
       </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
       <c r="D27">
-        <v>153461600</v>
+        <v>77440128</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <f>1+3+2+4</f>
-        <v>10</v>
+        <f>4/SUM(1,18,1,4)</f>
+        <v>0.16666666666666666</v>
       </c>
       <c r="G27">
-        <f t="shared" si="4"/>
-        <v>124</v>
+        <f>9/SUM(1,31,3,9)</f>
+        <v>0.20454545454545456</v>
       </c>
       <c r="H27">
-        <f t="shared" si="2"/>
-        <v>8.0645161290322578E-2</v>
+        <f>3/SUM(0,23,2,3)</f>
+        <v>0.10714285714285714</v>
       </c>
       <c r="I27">
-        <v>0.1</v>
+        <f>4/SUM(3,17,4,4)</f>
+        <v>0.14285714285714285</v>
       </c>
       <c r="J27">
-        <v>0.1</v>
+        <f t="shared" si="1"/>
+        <v>0.1553030303030303</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>4.0940000691293749E-2</v>
+      </c>
+      <c r="L27">
+        <v>0.15</v>
+      </c>
+      <c r="M27">
+        <v>0.15</v>
+      </c>
+      <c r="N27">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O27">
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="P27">
+        <v>0.14634146341463414</v>
+      </c>
+      <c r="Q27">
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="R27">
+        <v>0.14610139448733422</v>
+      </c>
+      <c r="S27">
+        <v>2.286822588113838E-3</v>
+      </c>
+      <c r="T27">
+        <v>0.08</v>
+      </c>
+      <c r="U27">
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="V27">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="W27">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="X27">
+        <v>0.14290051679586563</v>
+      </c>
+      <c r="Y27">
+        <v>4.6184322453183657E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
       </c>
       <c r="D28">
-        <v>148889089</v>
+        <v>1330530</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <f>18+31+23+17</f>
-        <v>89</v>
+        <f>0/SUM(1,18,1,4)</f>
+        <v>0</v>
       </c>
       <c r="G28">
-        <f t="shared" si="4"/>
-        <v>124</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="H28">
-        <f t="shared" si="2"/>
-        <v>0.717741935483871</v>
+        <f>0/SUM(0,23,2,3)</f>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0.65</v>
+        <f>0/SUM(3,17,4,4)</f>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>0.65</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0.1</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="F29">
-        <f>0+0+0+0</f>
+        <f>0/SUM(1,18,1,4)</f>
         <v>0</v>
       </c>
       <c r="G29">
-        <f t="shared" si="4"/>
-        <v>124</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="H29">
-        <f t="shared" si="2"/>
+        <f>0/SUM(0,23,2,3)</f>
         <v>0</v>
       </c>
       <c r="I29">
+        <f>0/SUM(3,17,4,4)</f>
         <v>0</v>
       </c>
       <c r="J29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="I13 H20 F25" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>